--- a/Models/CLIP/female1data/clip_big5_woman1_cropped.xlsx
+++ b/Models/CLIP/female1data/clip_big5_woman1_cropped.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/yq_c_tamu_edu/Documents/Research/genderBias/GenderBias-SRL-Implementation/Models/CLIP/female1data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_B1213419DBFA99A39E16E0AA2FB5155BF9BD9785" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE5EC478-7641-4D86-B24D-9754AC3A4A4B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Extraversion" sheetId="1" r:id="rId1"/>
@@ -13,12 +19,25 @@
     <sheet name="Neuroticism" sheetId="4" r:id="rId4"/>
     <sheet name="Openness" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Positive Trait</t>
   </si>
@@ -159,14 +178,25 @@
   </si>
   <si>
     <t>Likes to reflect, play with ideas</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -194,21 +224,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,7 +285,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -280,6 +319,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -314,9 +354,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -489,11 +530,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -507,62 +548,62 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.0565643273293972</v>
+        <v>5.6564327329397202E-2</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0.02070745453238487</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>2.0707454532384869E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.04193973541259766</v>
+        <v>4.1939735412597663E-2</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>0.002208070596680045</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2.2080705966800451E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.01136084739118814</v>
+        <v>1.1360847391188139E-2</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>0.001245713559910655</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.245713559910655E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.009971064515411854</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>9.9710645154118538E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6">
-        <v>0.006833622697740793</v>
+        <v>6.8336226977407932E-3</v>
       </c>
     </row>
   </sheetData>
@@ -571,11 +612,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -589,68 +630,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>0.03668270632624626</v>
+        <v>3.6682706326246262E-2</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
       <c r="D2">
-        <v>0.01693407073616982</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.6934070736169819E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>0.01058896910399199</v>
+        <v>1.0588969103991991E-2</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3">
-        <v>0.01356110069900751</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.3561100699007509E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>0.01011056080460548</v>
+        <v>1.0110560804605481E-2</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4">
-        <v>0.005015325266867876</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>5.0153252668678761E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>0.006861377041786909</v>
+        <v>6.8613770417869091E-3</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5">
-        <v>0.004372717812657356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>4.3727178126573563E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <v>0.00481886975467205</v>
+        <v>4.8188697546720496E-3</v>
       </c>
     </row>
   </sheetData>
@@ -659,11 +700,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,68 +718,68 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2">
-        <v>0.01844033412635326</v>
+        <v>1.844033412635326E-2</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2">
-        <v>0.006116759032011032</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>6.1167590320110321E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0.01794926822185516</v>
+        <v>1.794926822185516E-2</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
       <c r="D3">
-        <v>0.002868108684197068</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>2.8681086841970682E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0.003846879815682769</v>
+        <v>3.8468798156827688E-3</v>
       </c>
       <c r="C4" t="s">
         <v>28</v>
       </c>
       <c r="D4">
-        <v>0.001343540381640196</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>1.3435403816401961E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
       <c r="B5">
-        <v>0.00203584274277091</v>
+        <v>2.0358427427709098E-3</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>0.0007597948424518108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>7.5979484245181084E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6">
-        <v>0.001282421057112515</v>
+        <v>1.282421057112515E-3</v>
       </c>
     </row>
   </sheetData>
@@ -747,11 +788,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -765,62 +806,75 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
       <c r="B2">
-        <v>0.08015190064907074</v>
+        <v>8.015190064907074E-2</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
       </c>
       <c r="D2">
-        <v>0.01714820042252541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>1.7148200422525409E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>31</v>
       </c>
       <c r="B3">
-        <v>0.01625284738838673</v>
+        <v>1.625284738838673E-2</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3">
-        <v>0.007014423608779907</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>7.0144236087799072E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4">
-        <v>0.01350807584822178</v>
+        <v>1.3508075848221781E-2</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
       </c>
       <c r="D4">
-        <v>0.005792247131466866</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>5.7922471314668664E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>0.005752523429691792</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>5.7525234296917924E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>0.004837683867663145</v>
+        <v>4.8376838676631451E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1">
+        <f>AVERAGE(B2:B6)</f>
+        <v>3.6637607961893082E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <f>AVERAGE(D2:D6)</f>
+        <v>8.1090156920254237E-3</v>
       </c>
     </row>
   </sheetData>
@@ -829,11 +883,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -847,72 +901,72 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
       <c r="B2">
-        <v>0.2771541178226471</v>
+        <v>0.27715411782264709</v>
       </c>
       <c r="C2" t="s">
         <v>45</v>
       </c>
       <c r="D2">
-        <v>0.1067440658807755</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>0.10674406588077549</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>39</v>
       </c>
       <c r="B3">
-        <v>0.05141975730657578</v>
+        <v>5.1419757306575782E-2</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
       </c>
       <c r="D3">
-        <v>0.01194193121045828</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1.194193121045828E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4">
-        <v>0.0482269711792469</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>4.8226971179246902E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5">
-        <v>0.01979653723537922</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>1.9796537235379219E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
       <c r="B6">
-        <v>0.01523575838655233</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>1.523575838655233E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
       <c r="B7">
-        <v>0.002967805834487081</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>2.967805834487081E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>44</v>
       </c>
       <c r="B8">
-        <v>0.001635636552236974</v>
+        <v>1.635636552236974E-3</v>
       </c>
     </row>
   </sheetData>
